--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/77.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/77.xlsx
@@ -426,13 +426,13 @@
         <v>-4.525581293378582</v>
       </c>
       <c r="E2">
-        <v>-12.47812616383713</v>
+        <v>-15.97533984268873</v>
       </c>
       <c r="F2">
-        <v>-2.140392651246024</v>
+        <v>-2.405964296206065</v>
       </c>
       <c r="G2">
-        <v>-6.072140878434299</v>
+        <v>-5.614699627454424</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.102955774952676</v>
       </c>
       <c r="E3">
-        <v>-13.87700801259856</v>
+        <v>-18.96358021392223</v>
       </c>
       <c r="F3">
-        <v>-2.353329830106435</v>
+        <v>-2.13789356331146</v>
       </c>
       <c r="G3">
-        <v>-4.667807460675461</v>
+        <v>-6.746181192412069</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.856119356515554</v>
       </c>
       <c r="E4">
-        <v>-13.51002047901695</v>
+        <v>-18.12597101909348</v>
       </c>
       <c r="F4">
-        <v>-2.4862946113549</v>
+        <v>-2.287229112607823</v>
       </c>
       <c r="G4">
-        <v>-4.701614751722499</v>
+        <v>-7.449817783510925</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.817869540079225</v>
       </c>
       <c r="E5">
-        <v>-14.72385076592895</v>
+        <v>-16.67305088999852</v>
       </c>
       <c r="F5">
-        <v>-2.365598007980386</v>
+        <v>-1.845109891459381</v>
       </c>
       <c r="G5">
-        <v>-5.324606453484708</v>
+        <v>-6.203973422899156</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.946150158617119</v>
       </c>
       <c r="E6">
-        <v>-15.54991688051214</v>
+        <v>-18.7329586181336</v>
       </c>
       <c r="F6">
-        <v>-1.468538674445062</v>
+        <v>-1.866978494592727</v>
       </c>
       <c r="G6">
-        <v>-4.667350605391042</v>
+        <v>-6.106587104770416</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.2128499221519</v>
       </c>
       <c r="E7">
-        <v>-15.83899201879178</v>
+        <v>-17.97346107146316</v>
       </c>
       <c r="F7">
-        <v>-1.850066890974707</v>
+        <v>-1.941682694476963</v>
       </c>
       <c r="G7">
-        <v>-5.285376488844344</v>
+        <v>-8.203715076986995</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.576751502258971</v>
       </c>
       <c r="E8">
-        <v>-17.00876478208315</v>
+        <v>-19.08402856557824</v>
       </c>
       <c r="F8">
-        <v>-1.599782759216403</v>
+        <v>-1.968501962301973</v>
       </c>
       <c r="G8">
-        <v>-5.875554063221298</v>
+        <v>-7.310569617038101</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.993723543628941</v>
       </c>
       <c r="E9">
-        <v>-16.85453401432991</v>
+        <v>-19.05437611777602</v>
       </c>
       <c r="F9">
-        <v>-1.661337448884745</v>
+        <v>-1.076869197085902</v>
       </c>
       <c r="G9">
-        <v>-5.413928282679784</v>
+        <v>-7.413173354936732</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.413896852176975</v>
       </c>
       <c r="E10">
-        <v>-18.22714618537285</v>
+        <v>-22.47528500959838</v>
       </c>
       <c r="F10">
-        <v>-1.713878476335364</v>
+        <v>-1.372911343858998</v>
       </c>
       <c r="G10">
-        <v>-5.529171683447353</v>
+        <v>-8.035075887216522</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.802787471827731</v>
       </c>
       <c r="E11">
-        <v>-17.77565279833411</v>
+        <v>-20.99594576314266</v>
       </c>
       <c r="F11">
-        <v>-1.027703046941084</v>
+        <v>-1.978723200280219</v>
       </c>
       <c r="G11">
-        <v>-5.122924708686768</v>
+        <v>-6.47926845830833</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.126594758725279</v>
       </c>
       <c r="E12">
-        <v>-16.87208637958364</v>
+        <v>-21.30687984545732</v>
       </c>
       <c r="F12">
-        <v>-1.356672023402082</v>
+        <v>-1.905693769401559</v>
       </c>
       <c r="G12">
-        <v>-5.615368357653357</v>
+        <v>-7.142698473832737</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.357152323636035</v>
       </c>
       <c r="E13">
-        <v>-18.31409288632012</v>
+        <v>-21.40181477455413</v>
       </c>
       <c r="F13">
-        <v>-1.001224275887894</v>
+        <v>-1.460391299363084</v>
       </c>
       <c r="G13">
-        <v>-4.683923196360634</v>
+        <v>-8.323960712064403</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.487097764091888</v>
       </c>
       <c r="E14">
-        <v>-17.96533246061939</v>
+        <v>-21.13770964195278</v>
       </c>
       <c r="F14">
-        <v>-0.9465222817156581</v>
+        <v>-1.814018576927474</v>
       </c>
       <c r="G14">
-        <v>-4.61203469997536</v>
+        <v>-6.080559595740666</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.516293554595068</v>
       </c>
       <c r="E15">
-        <v>-18.77031852869688</v>
+        <v>-23.66924888103872</v>
       </c>
       <c r="F15">
-        <v>-0.5761005947709908</v>
+        <v>-1.501826589081684</v>
       </c>
       <c r="G15">
-        <v>-4.074901996774149</v>
+        <v>-6.12905246679991</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.450793492300146</v>
       </c>
       <c r="E16">
-        <v>-20.21629197866408</v>
+        <v>-23.52385769454845</v>
       </c>
       <c r="F16">
-        <v>-0.5564317591541906</v>
+        <v>-1.33538543219266</v>
       </c>
       <c r="G16">
-        <v>-3.722971142676386</v>
+        <v>-5.819662122881782</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.306843012933127</v>
       </c>
       <c r="E17">
-        <v>-20.36264773011798</v>
+        <v>-24.54493801379797</v>
       </c>
       <c r="F17">
-        <v>-0.1975711253922313</v>
+        <v>-0.4117206311309111</v>
       </c>
       <c r="G17">
-        <v>-4.551071003869681</v>
+        <v>-3.329969660618425</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.108146481578508</v>
       </c>
       <c r="E18">
-        <v>-21.42655835653204</v>
+        <v>-24.72844083753678</v>
       </c>
       <c r="F18">
-        <v>-0.2098076291478742</v>
+        <v>-0.7051472875846588</v>
       </c>
       <c r="G18">
-        <v>-2.835122555590325</v>
+        <v>-3.874567644010692</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.875964370327286</v>
       </c>
       <c r="E19">
-        <v>-21.44299218870587</v>
+        <v>-25.51077547862791</v>
       </c>
       <c r="F19">
-        <v>0.4955536055589972</v>
+        <v>-0.7304287769657763</v>
       </c>
       <c r="G19">
-        <v>-2.882039606972876</v>
+        <v>-1.98794733099975</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.62763295214278</v>
       </c>
       <c r="E20">
-        <v>-22.13485244759775</v>
+        <v>-26.80034449331819</v>
       </c>
       <c r="F20">
-        <v>0.1097968942351298</v>
+        <v>-0.6155974284490929</v>
       </c>
       <c r="G20">
-        <v>-2.779088261792621</v>
+        <v>-3.875329069484725</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.387776762452985</v>
       </c>
       <c r="E21">
-        <v>-23.0192815351918</v>
+        <v>-29.25064290870652</v>
       </c>
       <c r="F21">
-        <v>0.5964507175786867</v>
+        <v>-0.6451976838616139</v>
       </c>
       <c r="G21">
-        <v>-1.956563359287459</v>
+        <v>-3.670128214778539</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.172277194060485</v>
       </c>
       <c r="E22">
-        <v>-22.29189992618376</v>
+        <v>-26.43610574345924</v>
       </c>
       <c r="F22">
-        <v>0.5522922455384887</v>
+        <v>0.1797547274907942</v>
       </c>
       <c r="G22">
-        <v>-2.309292054860186</v>
+        <v>-2.633652685706898</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.987179587421767</v>
       </c>
       <c r="E23">
-        <v>-22.74004224245682</v>
+        <v>-29.47557674114151</v>
       </c>
       <c r="F23">
-        <v>1.391133757769301</v>
+        <v>-0.367901072156617</v>
       </c>
       <c r="G23">
-        <v>-2.154358523622295</v>
+        <v>-3.623260821579077</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.844489412292871</v>
       </c>
       <c r="E24">
-        <v>-23.64578232873097</v>
+        <v>-28.62642899454122</v>
       </c>
       <c r="F24">
-        <v>1.346044066650824</v>
+        <v>-0.1884854045553552</v>
       </c>
       <c r="G24">
-        <v>-2.568878551685518</v>
+        <v>-3.40049090169598</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.748406616676962</v>
       </c>
       <c r="E25">
-        <v>-25.98700339069655</v>
+        <v>-27.75376941089311</v>
       </c>
       <c r="F25">
-        <v>1.108060578737738</v>
+        <v>0.6318180380822804</v>
       </c>
       <c r="G25">
-        <v>-2.734134363914857</v>
+        <v>-3.997435231155203</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.694139105873712</v>
       </c>
       <c r="E26">
-        <v>-25.32168451796363</v>
+        <v>-30.62323696585343</v>
       </c>
       <c r="F26">
-        <v>1.18945831167358</v>
+        <v>-0.06705079422424698</v>
       </c>
       <c r="G26">
-        <v>-2.343059619360752</v>
+        <v>-4.248655979402797</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.6764752833227</v>
       </c>
       <c r="E27">
-        <v>-24.97963529074226</v>
+        <v>-30.03663655679584</v>
       </c>
       <c r="F27">
-        <v>0.8964188713161571</v>
+        <v>0.7354905947187775</v>
       </c>
       <c r="G27">
-        <v>-2.156814948412434</v>
+        <v>-3.639088539802333</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.690696046468976</v>
       </c>
       <c r="E28">
-        <v>-24.8273970515524</v>
+        <v>-29.51968634221323</v>
       </c>
       <c r="F28">
-        <v>1.647128733058679</v>
+        <v>-0.323694297085998</v>
       </c>
       <c r="G28">
-        <v>-3.33712374952879</v>
+        <v>-3.926695494072057</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.724111662586806</v>
       </c>
       <c r="E29">
-        <v>-25.32986294202148</v>
+        <v>-29.81281672896673</v>
       </c>
       <c r="F29">
-        <v>1.161303187908897</v>
+        <v>0.2459282954615161</v>
       </c>
       <c r="G29">
-        <v>-2.43105391979458</v>
+        <v>-3.352921672842192</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.759119378168468</v>
       </c>
       <c r="E30">
-        <v>-26.40487738670235</v>
+        <v>-27.58195910704209</v>
       </c>
       <c r="F30">
-        <v>1.870516787255075</v>
+        <v>0.2676203153852902</v>
       </c>
       <c r="G30">
-        <v>-2.946148321340863</v>
+        <v>-3.275670092683299</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.787466942300055</v>
       </c>
       <c r="E31">
-        <v>-25.91659467682529</v>
+        <v>-30.63064102085597</v>
       </c>
       <c r="F31">
-        <v>1.607319117462278</v>
+        <v>0.2962038316000991</v>
       </c>
       <c r="G31">
-        <v>-3.384285781281247</v>
+        <v>-4.230550605848523</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.795493662950045</v>
       </c>
       <c r="E32">
-        <v>-25.62933092814872</v>
+        <v>-29.91838677927055</v>
       </c>
       <c r="F32">
-        <v>1.799398889416351</v>
+        <v>0.5527048009294606</v>
       </c>
       <c r="G32">
-        <v>-2.949631015248176</v>
+        <v>-2.062014166349864</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.767834910761324</v>
       </c>
       <c r="E33">
-        <v>-26.16183871518468</v>
+        <v>-29.99705090125779</v>
       </c>
       <c r="F33">
-        <v>1.481031240353305</v>
+        <v>0.02493084534447613</v>
       </c>
       <c r="G33">
-        <v>-2.263013938766714</v>
+        <v>-3.942993309761889</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.698583920393647</v>
       </c>
       <c r="E34">
-        <v>-26.55212524753575</v>
+        <v>-29.09564682884599</v>
       </c>
       <c r="F34">
-        <v>1.780674734378111</v>
+        <v>0.5978396276665271</v>
       </c>
       <c r="G34">
-        <v>-3.583507790743509</v>
+        <v>-3.764439036101297</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.582921692640658</v>
       </c>
       <c r="E35">
-        <v>-25.75081630035249</v>
+        <v>-30.34129417413587</v>
       </c>
       <c r="F35">
-        <v>1.725986201706156</v>
+        <v>0.4102583723652595</v>
       </c>
       <c r="G35">
-        <v>-4.041253611912997</v>
+        <v>-3.021857187278456</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.416488425102457</v>
       </c>
       <c r="E36">
-        <v>-25.98187715811986</v>
+        <v>-29.5568039794171</v>
       </c>
       <c r="F36">
-        <v>1.537778590715332</v>
+        <v>0.304261727297855</v>
       </c>
       <c r="G36">
-        <v>-3.204860834143827</v>
+        <v>-3.335875673860485</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.200585680216695</v>
       </c>
       <c r="E37">
-        <v>-24.68071524996995</v>
+        <v>-30.5060310015869</v>
       </c>
       <c r="F37">
-        <v>1.41587282787438</v>
+        <v>0.8030815794838178</v>
       </c>
       <c r="G37">
-        <v>-3.244339089699637</v>
+        <v>-4.777790404581129</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.942211498256954</v>
       </c>
       <c r="E38">
-        <v>-25.52169815793441</v>
+        <v>-28.65269414378571</v>
       </c>
       <c r="F38">
-        <v>1.613050549170253</v>
+        <v>0.6076570206363362</v>
       </c>
       <c r="G38">
-        <v>-3.023866688420793</v>
+        <v>-3.372642592619631</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.647816558896826</v>
       </c>
       <c r="E39">
-        <v>-26.49505288961709</v>
+        <v>-29.50427368092812</v>
       </c>
       <c r="F39">
-        <v>1.712239634360141</v>
+        <v>0.6877608658392635</v>
       </c>
       <c r="G39">
-        <v>-2.862881479937114</v>
+        <v>-3.262378252343125</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.324223884455459</v>
       </c>
       <c r="E40">
-        <v>-25.6484456169351</v>
+        <v>-29.59893690158446</v>
       </c>
       <c r="F40">
-        <v>1.921428181318707</v>
+        <v>0.7053004088527554</v>
       </c>
       <c r="G40">
-        <v>-3.120763045809722</v>
+        <v>-3.057038354724291</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.985738774068327</v>
       </c>
       <c r="E41">
-        <v>-26.47891340825375</v>
+        <v>-28.34885618024107</v>
       </c>
       <c r="F41">
-        <v>1.513972323394446</v>
+        <v>0.7539233478685773</v>
       </c>
       <c r="G41">
-        <v>-3.165750049142878</v>
+        <v>-2.738203024382622</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.642188243100028</v>
       </c>
       <c r="E42">
-        <v>-26.26676798641641</v>
+        <v>-29.58757496029922</v>
       </c>
       <c r="F42">
-        <v>2.03006090488236</v>
+        <v>0.9050659056144564</v>
       </c>
       <c r="G42">
-        <v>-3.620109182225691</v>
+        <v>-2.524686079281787</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.300797188248418</v>
       </c>
       <c r="E43">
-        <v>-24.28761653526011</v>
+        <v>-27.96524461857731</v>
       </c>
       <c r="F43">
-        <v>1.935337870374012</v>
+        <v>0.7778357234857975</v>
       </c>
       <c r="G43">
-        <v>-2.190029651807941</v>
+        <v>-1.501181267633011</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.972623151705359</v>
       </c>
       <c r="E44">
-        <v>-24.65404253806477</v>
+        <v>-29.08352863240146</v>
       </c>
       <c r="F44">
-        <v>1.55527062255136</v>
+        <v>1.317133515164477</v>
       </c>
       <c r="G44">
-        <v>-2.318240459452836</v>
+        <v>-1.534382728846361</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.665440893810647</v>
       </c>
       <c r="E45">
-        <v>-25.23863683313696</v>
+        <v>-27.92375021124502</v>
       </c>
       <c r="F45">
-        <v>2.540853573789045</v>
+        <v>1.249366739042823</v>
       </c>
       <c r="G45">
-        <v>-1.532777114259815</v>
+        <v>-2.206807496600968</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.382832206144303</v>
       </c>
       <c r="E46">
-        <v>-24.39740485910207</v>
+        <v>-29.82778786403609</v>
       </c>
       <c r="F46">
-        <v>1.798470837749904</v>
+        <v>1.537558455593086</v>
       </c>
       <c r="G46">
-        <v>-2.713569255024905</v>
+        <v>-2.203735310340524</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.12834663397932</v>
       </c>
       <c r="E47">
-        <v>-23.5875869092584</v>
+        <v>-28.22416917691387</v>
       </c>
       <c r="F47">
-        <v>1.990257624109621</v>
+        <v>0.9576227701242299</v>
       </c>
       <c r="G47">
-        <v>-2.519038288591791</v>
+        <v>-1.82060256453513</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.9052970977428467</v>
       </c>
       <c r="E48">
-        <v>-24.0613694453629</v>
+        <v>-25.59901279466737</v>
       </c>
       <c r="F48">
-        <v>2.160927275792869</v>
+        <v>1.40098915968108</v>
       </c>
       <c r="G48">
-        <v>-2.593111745032984</v>
+        <v>-4.051903636912832</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.7124591884190538</v>
       </c>
       <c r="E49">
-        <v>-25.20022178812989</v>
+        <v>-25.63331598527547</v>
       </c>
       <c r="F49">
-        <v>2.22146126699871</v>
+        <v>0.6290671409071621</v>
       </c>
       <c r="G49">
-        <v>-2.16382999441015</v>
+        <v>-3.877825220821335</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.5462891883201716</v>
       </c>
       <c r="E50">
-        <v>-23.10922608593215</v>
+        <v>-25.04400754876129</v>
       </c>
       <c r="F50">
-        <v>1.525495367635183</v>
+        <v>1.217257101607288</v>
       </c>
       <c r="G50">
-        <v>-1.732859865562287</v>
+        <v>-4.098400249011896</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.4070278255977703</v>
       </c>
       <c r="E51">
-        <v>-22.31329696587</v>
+        <v>-26.96978640526319</v>
       </c>
       <c r="F51">
-        <v>2.390993817834672</v>
+        <v>1.275008521519703</v>
       </c>
       <c r="G51">
-        <v>-1.808605147500812</v>
+        <v>-3.526844493293343</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.2910731272592776</v>
       </c>
       <c r="E52">
-        <v>-22.16431469949165</v>
+        <v>-27.04118232646812</v>
       </c>
       <c r="F52">
-        <v>2.089898065485409</v>
+        <v>1.046913693342621</v>
       </c>
       <c r="G52">
-        <v>-1.864811589666558</v>
+        <v>-2.945317374410506</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1941954444351327</v>
       </c>
       <c r="E53">
-        <v>-22.96593611138145</v>
+        <v>-27.01091400620085</v>
       </c>
       <c r="F53">
-        <v>1.872532844885429</v>
+        <v>1.243445262624995</v>
       </c>
       <c r="G53">
-        <v>-0.8708401547736196</v>
+        <v>-2.589850857676801</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.1149009290689661</v>
       </c>
       <c r="E54">
-        <v>-22.36053347824401</v>
+        <v>-25.71423981579254</v>
       </c>
       <c r="F54">
-        <v>1.356914624054401</v>
+        <v>1.672559882648806</v>
       </c>
       <c r="G54">
-        <v>-1.121905307380868</v>
+        <v>-2.564591395212162</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.05108170201908773</v>
       </c>
       <c r="E55">
-        <v>-21.94298100389276</v>
+        <v>-25.87692524451809</v>
       </c>
       <c r="F55">
-        <v>1.955273560437564</v>
+        <v>0.7057200909203468</v>
       </c>
       <c r="G55">
-        <v>-2.214425061886831</v>
+        <v>-3.237926562990068</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.711554691618499E-05</v>
       </c>
       <c r="E56">
-        <v>-22.38661748852819</v>
+        <v>-25.56232762673123</v>
       </c>
       <c r="F56">
-        <v>2.268003216441645</v>
+        <v>1.33756173776773</v>
       </c>
       <c r="G56">
-        <v>-3.161598625036632</v>
+        <v>-3.08029824768321</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.04021645140600163</v>
       </c>
       <c r="E57">
-        <v>-21.67306131066556</v>
+        <v>-22.73853426061227</v>
       </c>
       <c r="F57">
-        <v>1.438619595937837</v>
+        <v>1.138982436736694</v>
       </c>
       <c r="G57">
-        <v>-2.914565716896216</v>
+        <v>-3.047947596673452</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.07083654354273497</v>
       </c>
       <c r="E58">
-        <v>-20.7959457085939</v>
+        <v>-23.91801607217608</v>
       </c>
       <c r="F58">
-        <v>1.741056747197478</v>
+        <v>0.8882073561446034</v>
       </c>
       <c r="G58">
-        <v>-2.541563240440992</v>
+        <v>-4.269591869393148</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.09421289187294578</v>
       </c>
       <c r="E59">
-        <v>-20.45011973405014</v>
+        <v>-22.70438956659444</v>
       </c>
       <c r="F59">
-        <v>2.452173961054013</v>
+        <v>1.218245334098523</v>
       </c>
       <c r="G59">
-        <v>-1.680549935496263</v>
+        <v>-3.918359540404172</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.1122547661934118</v>
       </c>
       <c r="E60">
-        <v>-21.93537769603388</v>
+        <v>-22.83115513949115</v>
       </c>
       <c r="F60">
-        <v>1.406411768735545</v>
+        <v>0.8724732378747125</v>
       </c>
       <c r="G60">
-        <v>-3.432450908332104</v>
+        <v>-3.644087463566632</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.1262273408929358</v>
       </c>
       <c r="E61">
-        <v>-20.82815221573645</v>
+        <v>-22.64366725862558</v>
       </c>
       <c r="F61">
-        <v>1.782956854602259</v>
+        <v>0.800289505954898</v>
       </c>
       <c r="G61">
-        <v>-2.429766117579804</v>
+        <v>-2.593896344325791</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.1386067816279398</v>
       </c>
       <c r="E62">
-        <v>-22.17731141989367</v>
+        <v>-23.60277993955413</v>
       </c>
       <c r="F62">
-        <v>1.270437946247745</v>
+        <v>1.077697768926933</v>
       </c>
       <c r="G62">
-        <v>-2.726093048799968</v>
+        <v>-4.376330478670329</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.1523786367344879</v>
       </c>
       <c r="E63">
-        <v>-20.03258990206892</v>
+        <v>-22.41974780436831</v>
       </c>
       <c r="F63">
-        <v>1.672563050060637</v>
+        <v>1.411755192494238</v>
       </c>
       <c r="G63">
-        <v>-2.646053989297008</v>
+        <v>-4.630090415346545</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.1707778170375772</v>
       </c>
       <c r="E64">
-        <v>-20.93061799710801</v>
+        <v>-22.69554092838345</v>
       </c>
       <c r="F64">
-        <v>1.139627005044278</v>
+        <v>0.7959121428046234</v>
       </c>
       <c r="G64">
-        <v>-2.305683560222381</v>
+        <v>-4.963876169343562</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.1986589106668525</v>
       </c>
       <c r="E65">
-        <v>-19.98639493871668</v>
+        <v>-23.65647405586308</v>
       </c>
       <c r="F65">
-        <v>1.450410286478284</v>
+        <v>-0.1489632315826061</v>
       </c>
       <c r="G65">
-        <v>-3.457647470431497</v>
+        <v>-4.566266407894935</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.2406704093482885</v>
       </c>
       <c r="E66">
-        <v>-20.1461051600192</v>
+        <v>-22.88606288683415</v>
       </c>
       <c r="F66">
-        <v>1.165466750760588</v>
+        <v>1.163086440769682</v>
       </c>
       <c r="G66">
-        <v>-3.197385622316153</v>
+        <v>-3.597153859456385</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.2992289746154721</v>
       </c>
       <c r="E67">
-        <v>-19.90424842021754</v>
+        <v>-21.39614965357053</v>
       </c>
       <c r="F67">
-        <v>1.547611820744295</v>
+        <v>0.2873065717671603</v>
       </c>
       <c r="G67">
-        <v>-2.490633807864844</v>
+        <v>-5.648030199943807</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.3768859283830202</v>
       </c>
       <c r="E68">
-        <v>-19.92182342784131</v>
+        <v>-20.17347072844755</v>
       </c>
       <c r="F68">
-        <v>1.199329550644514</v>
+        <v>0.6131493127510802</v>
       </c>
       <c r="G68">
-        <v>-3.610962144900685</v>
+        <v>-4.689186963768075</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.4740053973492174</v>
       </c>
       <c r="E69">
-        <v>-19.52417359675377</v>
+        <v>-21.32287441565241</v>
       </c>
       <c r="F69">
-        <v>1.252066957628647</v>
+        <v>-0.08711634817286477</v>
       </c>
       <c r="G69">
-        <v>-3.817447491276107</v>
+        <v>-4.839551942161772</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.5885052119430122</v>
       </c>
       <c r="E70">
-        <v>-19.33133305961113</v>
+        <v>-21.86660828975339</v>
       </c>
       <c r="F70">
-        <v>1.135655070608355</v>
+        <v>0.3429643324593642</v>
       </c>
       <c r="G70">
-        <v>-2.888260122041167</v>
+        <v>-4.835691846062982</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.7185245922424649</v>
       </c>
       <c r="E71">
-        <v>-19.43386223961879</v>
+        <v>-22.12774274340571</v>
       </c>
       <c r="F71">
-        <v>0.8894632349355469</v>
+        <v>0.687027610000415</v>
       </c>
       <c r="G71">
-        <v>-4.224879641339752</v>
+        <v>-6.362482343319461</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.8633829930183585</v>
       </c>
       <c r="E72">
-        <v>-20.91569667525274</v>
+        <v>-20.52591280351652</v>
       </c>
       <c r="F72">
-        <v>0.7548624854764329</v>
+        <v>0.01030532121539283</v>
       </c>
       <c r="G72">
-        <v>-4.015510809799624</v>
+        <v>-5.296589306585856</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.020765124721927</v>
       </c>
       <c r="E73">
-        <v>-18.29870060316805</v>
+        <v>-21.28679606323331</v>
       </c>
       <c r="F73">
-        <v>0.8726236899366793</v>
+        <v>0.550511368236577</v>
       </c>
       <c r="G73">
-        <v>-3.935686935756717</v>
+        <v>-4.816057000469565</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.185474916726786</v>
       </c>
       <c r="E74">
-        <v>-19.4596066143524</v>
+        <v>-22.26586120063965</v>
       </c>
       <c r="F74">
-        <v>0.523030111338914</v>
+        <v>0.2522924176827095</v>
       </c>
       <c r="G74">
-        <v>-3.23042155625254</v>
+        <v>-5.680824464055827</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.353480317575895</v>
       </c>
       <c r="E75">
-        <v>-19.72618429376193</v>
+        <v>-21.36402918743412</v>
       </c>
       <c r="F75">
-        <v>0.6226135393017463</v>
+        <v>-0.890025948741229</v>
       </c>
       <c r="G75">
-        <v>-3.726510115857867</v>
+        <v>-5.21739443619541</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.51873802916828</v>
       </c>
       <c r="E76">
-        <v>-21.12879307663168</v>
+        <v>-23.47632230288994</v>
       </c>
       <c r="F76">
-        <v>0.6751260600458876</v>
+        <v>0.1086732548881255</v>
       </c>
       <c r="G76">
-        <v>-3.469975942019743</v>
+        <v>-5.24992054611875</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.673130736399834</v>
       </c>
       <c r="E77">
-        <v>-20.60142510759442</v>
+        <v>-23.06251940501704</v>
       </c>
       <c r="F77">
-        <v>0.8955383308271727</v>
+        <v>-0.2854414644044736</v>
       </c>
       <c r="G77">
-        <v>-3.512470104561828</v>
+        <v>-6.138484211041294</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.810290052267933</v>
       </c>
       <c r="E78">
-        <v>-21.58817506539178</v>
+        <v>-22.19701481030104</v>
       </c>
       <c r="F78">
-        <v>0.5005082295154496</v>
+        <v>0.3549331899152978</v>
       </c>
       <c r="G78">
-        <v>-4.006810696122419</v>
+        <v>-5.593909401467801</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.923880328662978</v>
       </c>
       <c r="E79">
-        <v>-20.94045837112668</v>
+        <v>-23.84285246059677</v>
       </c>
       <c r="F79">
-        <v>0.2373026411930751</v>
+        <v>0.004575473213332912</v>
       </c>
       <c r="G79">
-        <v>-4.24582877351226</v>
+        <v>-6.466334156886398</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.007394830616727</v>
       </c>
       <c r="E80">
-        <v>-21.46769048594371</v>
+        <v>-23.29866573909502</v>
       </c>
       <c r="F80">
-        <v>0.7947924627224077</v>
+        <v>-0.05523080512436466</v>
       </c>
       <c r="G80">
-        <v>-4.172625990547895</v>
+        <v>-6.460169921092275</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.055730723416401</v>
       </c>
       <c r="E81">
-        <v>-21.40998867013797</v>
+        <v>-23.39310706452499</v>
       </c>
       <c r="F81">
-        <v>0.6825805637898611</v>
+        <v>-0.3308344352057568</v>
       </c>
       <c r="G81">
-        <v>-4.460729526648509</v>
+        <v>-5.144353869962471</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.063448257217278</v>
       </c>
       <c r="E82">
-        <v>-22.56516163322861</v>
+        <v>-25.10873302775293</v>
       </c>
       <c r="F82">
-        <v>0.1555549092499217</v>
+        <v>-0.8402381940246013</v>
       </c>
       <c r="G82">
-        <v>-2.974264784605893</v>
+        <v>-5.999517440939307</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.023912975754353</v>
       </c>
       <c r="E83">
-        <v>-24.22121552088564</v>
+        <v>-25.72522589373515</v>
       </c>
       <c r="F83">
-        <v>0.6061192421924445</v>
+        <v>-0.5180759855881627</v>
       </c>
       <c r="G83">
-        <v>-3.669214504209701</v>
+        <v>-5.65891527367693</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.932405218061609</v>
       </c>
       <c r="E84">
-        <v>-24.04716815087484</v>
+        <v>-25.19267735043311</v>
       </c>
       <c r="F84">
-        <v>0.6789111171837878</v>
+        <v>-0.02458134454286504</v>
       </c>
       <c r="G84">
-        <v>-3.821728026658385</v>
+        <v>-5.326440495713464</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.782266301899168</v>
       </c>
       <c r="E85">
-        <v>-26.64990858678338</v>
+        <v>-24.17361673059102</v>
       </c>
       <c r="F85">
-        <v>0.5816715739758058</v>
+        <v>-0.03158211654206512</v>
       </c>
       <c r="G85">
-        <v>-3.003741882087564</v>
+        <v>-4.698228063635824</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.566374560977659</v>
       </c>
       <c r="E86">
-        <v>-27.28876758588948</v>
+        <v>-26.05177868290226</v>
       </c>
       <c r="F86">
-        <v>0.7411111670126722</v>
+        <v>-0.3281492618261292</v>
       </c>
       <c r="G86">
-        <v>-2.739414684049995</v>
+        <v>-5.873561114806656</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.280310538668725</v>
       </c>
       <c r="E87">
-        <v>-28.72072088032893</v>
+        <v>-27.7274363345385</v>
       </c>
       <c r="F87">
-        <v>0.5685268148776584</v>
+        <v>-0.4609176635410798</v>
       </c>
       <c r="G87">
-        <v>-4.206827236514106</v>
+        <v>-5.104839198405729</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.9195400391191721</v>
       </c>
       <c r="E88">
-        <v>-29.74601494464259</v>
+        <v>-29.8071312298501</v>
       </c>
       <c r="F88">
-        <v>0.7543161069356062</v>
+        <v>-0.1734417820645959</v>
       </c>
       <c r="G88">
-        <v>-3.890835664790671</v>
+        <v>-4.263639508513538</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.4768166542464859</v>
       </c>
       <c r="E89">
-        <v>-30.70667409944475</v>
+        <v>-31.67941748713639</v>
       </c>
       <c r="F89">
-        <v>0.7935603395201958</v>
+        <v>-0.00132462317463675</v>
       </c>
       <c r="G89">
-        <v>-3.653625145265273</v>
+        <v>-4.970255590597738</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.05141342324664731</v>
       </c>
       <c r="E90">
-        <v>-32.42460052746859</v>
+        <v>-31.81369806264884</v>
       </c>
       <c r="F90">
-        <v>0.6454901712502692</v>
+        <v>-1.105607916480424</v>
       </c>
       <c r="G90">
-        <v>-2.236417015904209</v>
+        <v>-3.834284925888841</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.6620244079079184</v>
       </c>
       <c r="E91">
-        <v>-33.85639306108077</v>
+        <v>-34.4731893348215</v>
       </c>
       <c r="F91">
-        <v>1.029439082271663</v>
+        <v>-0.04998715483834465</v>
       </c>
       <c r="G91">
-        <v>-3.717310109804232</v>
+        <v>-4.292891488898539</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.357966790824065</v>
       </c>
       <c r="E92">
-        <v>-35.77177001278704</v>
+        <v>-35.87236779863044</v>
       </c>
       <c r="F92">
-        <v>1.162871056765182</v>
+        <v>-0.07924770533200388</v>
       </c>
       <c r="G92">
-        <v>-1.912748289075205</v>
+        <v>-4.169030738092246</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.138328261872283</v>
       </c>
       <c r="E93">
-        <v>-36.64097663500431</v>
+        <v>-38.04544435645421</v>
       </c>
       <c r="F93">
-        <v>0.8271998368700451</v>
+        <v>0.5263036314661272</v>
       </c>
       <c r="G93">
-        <v>-3.414312429322437</v>
+        <v>-3.463834880044395</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.988881186170024</v>
       </c>
       <c r="E94">
-        <v>-38.97699900880908</v>
+        <v>-39.22466351652558</v>
       </c>
       <c r="F94">
-        <v>0.7127200710665892</v>
+        <v>0.04992410024898377</v>
       </c>
       <c r="G94">
-        <v>-1.83677457949447</v>
+        <v>-4.335716705994551</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.904302582581149</v>
       </c>
       <c r="E95">
-        <v>-40.88218236552409</v>
+        <v>-41.53604646325461</v>
       </c>
       <c r="F95">
-        <v>0.7419061873822228</v>
+        <v>0.07444065967294414</v>
       </c>
       <c r="G95">
-        <v>-3.680609401955872</v>
+        <v>-3.854552085680259</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.882353478676658</v>
       </c>
       <c r="E96">
-        <v>-43.97176319233824</v>
+        <v>-42.05080489641751</v>
       </c>
       <c r="F96">
-        <v>1.203942885976189</v>
+        <v>0.009575232788375247</v>
       </c>
       <c r="G96">
-        <v>-2.803390976596411</v>
+        <v>-4.349948741267878</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.896965138060088</v>
       </c>
       <c r="E97">
-        <v>-45.89537517402747</v>
+        <v>-45.89603633123259</v>
       </c>
       <c r="F97">
-        <v>0.956783405989047</v>
+        <v>0.03213829096564105</v>
       </c>
       <c r="G97">
-        <v>-2.806959744687745</v>
+        <v>-3.534574617127542</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.949239275222928</v>
       </c>
       <c r="E98">
-        <v>-47.35883759061229</v>
+        <v>-48.24042958924054</v>
       </c>
       <c r="F98">
-        <v>0.992115884962501</v>
+        <v>0.430841798148226</v>
       </c>
       <c r="G98">
-        <v>-3.508302127727885</v>
+        <v>-5.645534048607196</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.000889735796717</v>
       </c>
       <c r="E99">
-        <v>-51.08427730250246</v>
+        <v>-47.63045772582937</v>
       </c>
       <c r="F99">
-        <v>0.6256827613658681</v>
+        <v>-0.09060446045162016</v>
       </c>
       <c r="G99">
-        <v>-2.586983925239792</v>
+        <v>-4.824399575228528</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.076074841752149</v>
       </c>
       <c r="E100">
-        <v>-52.89079653177536</v>
+        <v>-49.22686821444987</v>
       </c>
       <c r="F100">
-        <v>0.613245918811922</v>
+        <v>-0.02957081002945701</v>
       </c>
       <c r="G100">
-        <v>-3.316068679899025</v>
+        <v>-4.834043194384425</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.08254219632637</v>
       </c>
       <c r="E101">
-        <v>-52.95857080589266</v>
+        <v>-53.97181460087189</v>
       </c>
       <c r="F101">
-        <v>0.5147006100766601</v>
+        <v>0.1307350701431547</v>
       </c>
       <c r="G101">
-        <v>-4.560943050667787</v>
+        <v>-5.049569640627597</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.12206930346497</v>
       </c>
       <c r="E102">
-        <v>-56.34678298326113</v>
+        <v>-55.79111431591294</v>
       </c>
       <c r="F102">
-        <v>0.7309089335054112</v>
+        <v>0.08577603476270199</v>
       </c>
       <c r="G102">
-        <v>-3.374628919943193</v>
+        <v>-5.871518508208926</v>
       </c>
     </row>
   </sheetData>
